--- a/0. Absen.xlsx
+++ b/0. Absen.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\persiapan-rkt-2026\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E35161-1503-4FD9-A9D9-6EE03A89A9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -32,9 +26,41 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>KEHADIRAN PESERTA RAPAT</t>
+  </si>
+  <si>
+    <t>IN-HOUSE TRAINING &amp; RAPAT KERJA TAHUNAN</t>
+  </si>
+  <si>
+    <t>MADRASAH AL-QURAN BAITUL IZZAH</t>
+  </si>
+  <si>
+    <t>Nomor</t>
+  </si>
+  <si>
+    <t>Nama</t>
+  </si>
+  <si>
+    <t>Waktu Kedatangan</t>
+  </si>
+  <si>
+    <t>Tanda Tangan</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -42,16 +68,354 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -59,24 +423,345 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -334,15 +1019,530 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B570A9A1-6404-4212-9FC3-086DC13FE64F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E84"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="7.71428571428571" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="3" max="3" width="20.2857142857143" customWidth="1"/>
+    <col min="4" max="5" width="16.1428571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:5">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:5">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:5">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:5">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:5">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:5">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:5">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:5">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:5">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:5">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:5">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:5">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:5">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:5">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:5">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:5">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:5">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:5">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:5">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:5">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:5">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:5">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:5">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:5">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:5">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:5">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:5">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:5">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:5">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:5">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="1:5">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="7"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="1:5">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:5">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="7"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" spans="1:5">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="7"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" spans="1:5">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="7"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:5">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="7"/>
+    </row>
+    <row r="42" ht="18" customHeight="1" spans="1:5">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="7"/>
+    </row>
+    <row r="43" ht="18" customHeight="1" spans="1:5">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="7"/>
+    </row>
+    <row r="44" ht="18" customHeight="1" spans="1:5">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+    </row>
+    <row r="45" ht="18" customHeight="1" spans="1:5">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+    </row>
+    <row r="46" ht="18" customHeight="1" spans="1:5">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+    </row>
+    <row r="47" ht="18" customHeight="1" spans="1:5">
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+    </row>
+    <row r="48" ht="18" customHeight="1" spans="1:5">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+    </row>
+    <row r="49" ht="18" customHeight="1" spans="1:5">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+    </row>
+    <row r="50" ht="18" customHeight="1" spans="1:5">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+    </row>
+    <row r="51" ht="18" customHeight="1" spans="1:5">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+    </row>
+    <row r="52" ht="18" customHeight="1" spans="1:5">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+    </row>
+    <row r="53" ht="18" customHeight="1" spans="1:5">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" ht="18" customHeight="1" spans="1:5">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+    </row>
+    <row r="55" ht="18" customHeight="1" spans="1:5">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+    </row>
+    <row r="56" ht="18" customHeight="1" spans="1:5">
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+    </row>
+    <row r="57" ht="18" customHeight="1" spans="1:5">
+      <c r="A57" s="6"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+    </row>
+    <row r="58" ht="18" customHeight="1" spans="1:5">
+      <c r="A58" s="6"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+    </row>
+    <row r="59" ht="18" customHeight="1" spans="1:5">
+      <c r="A59" s="6"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+    </row>
+    <row r="60" ht="18" customHeight="1" spans="1:5">
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+    </row>
+    <row r="61" ht="18" customHeight="1" spans="1:5">
+      <c r="A61" s="6"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+    </row>
+    <row r="62" ht="18" customHeight="1" spans="1:5">
+      <c r="A62" s="6"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+    </row>
+    <row r="63" ht="18" customHeight="1" spans="1:5">
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+    </row>
+    <row r="64" ht="18" customHeight="1"/>
+    <row r="65" ht="18" customHeight="1"/>
+    <row r="66" ht="18" customHeight="1"/>
+    <row r="67" ht="18" customHeight="1"/>
+    <row r="68" ht="18" customHeight="1"/>
+    <row r="69" ht="18" customHeight="1"/>
+    <row r="70" ht="18" customHeight="1"/>
+    <row r="71" ht="18" customHeight="1"/>
+    <row r="72" ht="18" customHeight="1"/>
+    <row r="73" ht="18" customHeight="1"/>
+    <row r="74" ht="18" customHeight="1"/>
+    <row r="75" ht="18" customHeight="1"/>
+    <row r="76" ht="18" customHeight="1"/>
+    <row r="77" ht="18" customHeight="1"/>
+    <row r="78" ht="18" customHeight="1"/>
+    <row r="79" ht="18" customHeight="1"/>
+    <row r="80" ht="18" customHeight="1"/>
+    <row r="81" ht="18" customHeight="1"/>
+    <row r="82" ht="18" customHeight="1"/>
+    <row r="83" ht="18" customHeight="1"/>
+    <row r="84" ht="18" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="E41:E42"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/0. Absen.xlsx
+++ b/0. Absen.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$E$63</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -684,19 +687,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1024,7 +1021,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
@@ -1047,10 +1046,10 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
@@ -1062,425 +1061,425 @@
       <c r="E3" s="1"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="3"/>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:5">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:5">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:5">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:5">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:5">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:5">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:5">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:5">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:5">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:5">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:5">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:5">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:5">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:5">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:5">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:5">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:5">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:5">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:5">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:5">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:5">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:5">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:5">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:5">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:5">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:5">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:5">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:5">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:5">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:5">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="7"/>
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:5">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="7"/>
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:5">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="7"/>
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
     </row>
     <row r="38" ht="18" customHeight="1" spans="1:5">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="7"/>
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:5">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="7"/>
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:5">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="7"/>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
     </row>
     <row r="41" ht="18" customHeight="1" spans="1:5">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="7"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
     </row>
     <row r="42" ht="18" customHeight="1" spans="1:5">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="7"/>
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:5">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="7"/>
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
     </row>
     <row r="44" ht="18" customHeight="1" spans="1:5">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
     </row>
     <row r="45" ht="18" customHeight="1" spans="1:5">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
     </row>
     <row r="46" ht="18" customHeight="1" spans="1:5">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
     </row>
     <row r="47" ht="18" customHeight="1" spans="1:5">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
     </row>
     <row r="48" ht="18" customHeight="1" spans="1:5">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
     </row>
     <row r="49" ht="18" customHeight="1" spans="1:5">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
     </row>
     <row r="50" ht="18" customHeight="1" spans="1:5">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
     </row>
     <row r="51" ht="18" customHeight="1" spans="1:5">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
     </row>
     <row r="52" ht="18" customHeight="1" spans="1:5">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
     </row>
     <row r="53" ht="18" customHeight="1" spans="1:5">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
     </row>
     <row r="54" ht="18" customHeight="1" spans="1:5">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
     </row>
     <row r="55" ht="18" customHeight="1" spans="1:5">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
     </row>
     <row r="56" ht="18" customHeight="1" spans="1:5">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
     </row>
     <row r="57" ht="18" customHeight="1" spans="1:5">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
     </row>
     <row r="58" ht="18" customHeight="1" spans="1:5">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
     </row>
     <row r="59" ht="18" customHeight="1" spans="1:5">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
     </row>
     <row r="60" ht="18" customHeight="1" spans="1:5">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
     </row>
     <row r="61" ht="18" customHeight="1" spans="1:5">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
     </row>
     <row r="62" ht="18" customHeight="1" spans="1:5">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
     </row>
     <row r="63" ht="18" customHeight="1" spans="1:5">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="4"/>
     </row>
     <row r="64" ht="18" customHeight="1"/>
     <row r="65" ht="18" customHeight="1"/>
@@ -1504,7 +1503,7 @@
     <row r="83" ht="18" customHeight="1"/>
     <row r="84" ht="18" customHeight="1"/>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="61">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
@@ -1523,6 +1522,21 @@
     <mergeCell ref="D28:D29"/>
     <mergeCell ref="D30:D31"/>
     <mergeCell ref="D32:D33"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="D62:D63"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="E11:E12"/>
@@ -1541,8 +1555,20 @@
     <mergeCell ref="E37:E38"/>
     <mergeCell ref="E39:E40"/>
     <mergeCell ref="E41:E42"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="E61:E62"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="90" fitToHeight="0" orientation="portrait" horizontalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>